--- a/supplementary/Table S6 - res.annot.categorized.xlsx
+++ b/supplementary/Table S6 - res.annot.categorized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341D9B23-03AC-46B7-BBF9-5283722F7EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D705D2-B992-436A-A9B6-BA410788FCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6930" yWindow="7110" windowWidth="26430" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6570" yWindow="8400" windowWidth="26430" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="res.annot.categorized" sheetId="1" r:id="rId1"/>
@@ -3210,11 +3210,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
       <t xml:space="preserve">Supplementary Table 6. Significant differentially expressed genes between HF and NF </t>
     </r>
     <r>
@@ -3722,10 +3717,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3956,19 +3951,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>1033</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -3979,17 +3974,17 @@
       <c r="S1" s="2"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -4000,17 +3995,17 @@
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -4021,17 +4016,17 @@
       <c r="S3" s="2"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -4042,17 +4037,17 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -4063,17 +4058,17 @@
       <c r="S5" s="2"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -4084,17 +4079,17 @@
       <c r="S6" s="2"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -4105,17 +4100,17 @@
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
